--- a/data/trans_dic/P32D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 15,21</t>
+          <t>6,99; 14,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,14</t>
+          <t>3,81; 10,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 12,46</t>
+          <t>6,7; 12,15</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,83</t>
+          <t>4,61; 9,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,73</t>
+          <t>7,42; 15,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,54</t>
+          <t>6,05; 10,66</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,03</t>
+          <t>4,77; 11,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,04; 4,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,61</t>
+          <t>1,46; 6,59</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 15,66</t>
+          <t>9,54; 16,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,3</t>
+          <t>3,67; 10,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,5</t>
+          <t>7,82; 12,48</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,89</t>
+          <t>7,78; 10,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,49</t>
+          <t>2,69; 7,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,91</t>
+          <t>5,67; 8,93</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24320; 50509</t>
+          <t>23211; 46908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6326; 17709</t>
+          <t>6052; 17077</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33310; 61204</t>
+          <t>32896; 59676</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21298; 46574</t>
+          <t>21859; 46183</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14390; 31705</t>
+          <t>14949; 32145</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39188; 71227</t>
+          <t>40845; 72020</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15744; 35927</t>
+          <t>15539; 36376</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 16089</t>
+          <t>154; 15755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11603; 46324</t>
+          <t>10221; 46199</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39595; 68797</t>
+          <t>41906; 71447</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10921; 29713</t>
+          <t>10582; 29140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55666; 90964</t>
+          <t>56904; 90797</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>122651; 171136</t>
+          <t>122231; 171466</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28096; 76684</t>
+          <t>27570; 76004</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>149926; 231208</t>
+          <t>147196; 231696</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 14,12</t>
+          <t>6,78; 14,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,75</t>
+          <t>3,63; 10,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,15</t>
+          <t>6,4; 11,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,75</t>
+          <t>5,52; 11,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,94</t>
+          <t>7,59; 15,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,66</t>
+          <t>6,61; 11,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 11,17</t>
+          <t>5,78; 12,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,2</t>
+          <t>1,17; 7,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 6,59</t>
+          <t>4,47; 9,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,26</t>
+          <t>9,68; 16,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 10,1</t>
+          <t>4,24; 11,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,48</t>
+          <t>8,2; 13,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,91</t>
+          <t>8,12; 11,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,42</t>
+          <t>5,63; 9,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,93</t>
+          <t>7,65; 10,07</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44959</t>
+          <t>46075</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23211; 46908</t>
+          <t>23897; 51211</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6052; 17077</t>
+          <t>6246; 18317</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32896; 59676</t>
+          <t>33578; 62562</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>38849</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53590</t>
+          <t>64042</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21859; 46183</t>
+          <t>27494; 55977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14949; 32145</t>
+          <t>16990; 35412</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40845; 72020</t>
+          <t>47726; 83445</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28704</t>
+          <t>36385</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15539; 36376</t>
+          <t>20836; 44067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>154; 15755</t>
+          <t>2348; 14817</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10221; 46199</t>
+          <t>25096; 51949</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>54018</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71572</t>
+          <t>79167</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41906; 71447</t>
+          <t>44636; 76145</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10582; 29140</t>
+          <t>13062; 34586</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56904; 90797</t>
+          <t>63050; 101500</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>122231; 171466</t>
+          <t>135843; 191270</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27570; 76004</t>
+          <t>50900; 82942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147196; 231696</t>
+          <t>197117; 259529</t>
         </is>
       </c>
     </row>
